--- a/data/nzd0182/nzd0182.xlsx
+++ b/data/nzd0182/nzd0182.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I571"/>
+  <dimension ref="A1:I572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19172,7 +19172,7 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>477.09</v>
+        <v>487.01</v>
       </c>
       <c r="C571" t="n">
         <v>352.78</v>
@@ -19193,6 +19193,39 @@
         <v>367.8</v>
       </c>
       <c r="I571" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>504.67</v>
+      </c>
+      <c r="C572" t="n">
+        <v>354.1</v>
+      </c>
+      <c r="D572" t="n">
+        <v>350.65</v>
+      </c>
+      <c r="E572" t="n">
+        <v>352.52</v>
+      </c>
+      <c r="F572" t="n">
+        <v>355.13</v>
+      </c>
+      <c r="G572" t="n">
+        <v>351.87</v>
+      </c>
+      <c r="H572" t="n">
+        <v>355.34</v>
+      </c>
+      <c r="I572" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -19209,7 +19242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B618"/>
+  <dimension ref="A1:B619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25392,6 +25425,16 @@
       </c>
       <c r="B618" t="n">
         <v>0.89</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -25560,28 +25603,28 @@
         <v>0.0154</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08965806491766974</v>
+        <v>-0.06847532509849802</v>
       </c>
       <c r="J2" t="n">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="K2" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003189915186576631</v>
+        <v>0.000186068757936142</v>
       </c>
       <c r="M2" t="n">
-        <v>31.54902431708188</v>
+        <v>31.61740946308771</v>
       </c>
       <c r="N2" t="n">
-        <v>1533.294772475458</v>
+        <v>1536.508142650632</v>
       </c>
       <c r="O2" t="n">
-        <v>39.15730803407529</v>
+        <v>39.19831810997294</v>
       </c>
       <c r="P2" t="n">
-        <v>455.211713984194</v>
+        <v>455.0050832511822</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25638,28 +25681,28 @@
         <v>0.0462</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7044921798675582</v>
+        <v>0.7085873247826666</v>
       </c>
       <c r="J3" t="n">
+        <v>571</v>
+      </c>
+      <c r="K3" t="n">
         <v>570</v>
       </c>
-      <c r="K3" t="n">
-        <v>569</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.2537125848824865</v>
+        <v>0.2560965886801998</v>
       </c>
       <c r="M3" t="n">
-        <v>7.865004582601554</v>
+        <v>7.871277472761859</v>
       </c>
       <c r="N3" t="n">
-        <v>85.07006816250694</v>
+        <v>85.17119000443725</v>
       </c>
       <c r="O3" t="n">
-        <v>9.223343654147715</v>
+        <v>9.228823868968204</v>
       </c>
       <c r="P3" t="n">
-        <v>323.5309021444494</v>
+        <v>323.4904332145703</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25716,28 +25759,28 @@
         <v>0.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.743009033050653</v>
+        <v>0.7459254443505616</v>
       </c>
       <c r="J4" t="n">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="K4" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2786504977655904</v>
+        <v>0.2807100763848444</v>
       </c>
       <c r="M4" t="n">
-        <v>7.204872133873217</v>
+        <v>7.209831202806087</v>
       </c>
       <c r="N4" t="n">
-        <v>82.77514272551937</v>
+        <v>82.75563095988505</v>
       </c>
       <c r="O4" t="n">
-        <v>9.098084563550691</v>
+        <v>9.097012199611752</v>
       </c>
       <c r="P4" t="n">
-        <v>322.5531580173817</v>
+        <v>322.5241937942164</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25794,28 +25837,28 @@
         <v>0.057</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8656149252926358</v>
+        <v>0.866579947537011</v>
       </c>
       <c r="J5" t="n">
+        <v>571</v>
+      </c>
+      <c r="K5" t="n">
         <v>570</v>
       </c>
-      <c r="K5" t="n">
-        <v>569</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.3674078646813247</v>
+        <v>0.3687937873725903</v>
       </c>
       <c r="M5" t="n">
-        <v>6.943980800473499</v>
+        <v>6.936634177878799</v>
       </c>
       <c r="N5" t="n">
-        <v>74.67876943836279</v>
+        <v>74.56152749719324</v>
       </c>
       <c r="O5" t="n">
-        <v>8.641687881332141</v>
+        <v>8.634901707442491</v>
       </c>
       <c r="P5" t="n">
-        <v>326.864033069339</v>
+        <v>326.8544519506864</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25872,28 +25915,28 @@
         <v>0.0359</v>
       </c>
       <c r="I6" t="n">
-        <v>0.882396257243708</v>
+        <v>0.8826869791472011</v>
       </c>
       <c r="J6" t="n">
+        <v>571</v>
+      </c>
+      <c r="K6" t="n">
         <v>570</v>
       </c>
-      <c r="K6" t="n">
-        <v>569</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.2746381177755148</v>
+        <v>0.275548045913678</v>
       </c>
       <c r="M6" t="n">
-        <v>9.017604084013925</v>
+        <v>9.003186244191781</v>
       </c>
       <c r="N6" t="n">
-        <v>119.0401790342475</v>
+        <v>118.8325866534211</v>
       </c>
       <c r="O6" t="n">
-        <v>10.91055356222807</v>
+        <v>10.90103603578216</v>
       </c>
       <c r="P6" t="n">
-        <v>330.9920132215394</v>
+        <v>330.9891268206625</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25950,28 +25993,28 @@
         <v>0.0523</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9227078851988428</v>
+        <v>0.9235617643485767</v>
       </c>
       <c r="J7" t="n">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="K7" t="n">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L7" t="n">
-        <v>0.214746007806128</v>
+        <v>0.2157080870044646</v>
       </c>
       <c r="M7" t="n">
-        <v>10.76675917345264</v>
+        <v>10.7526791942631</v>
       </c>
       <c r="N7" t="n">
-        <v>181.1262287862249</v>
+        <v>180.8198817690829</v>
       </c>
       <c r="O7" t="n">
-        <v>13.45831448533674</v>
+        <v>13.44692833955335</v>
       </c>
       <c r="P7" t="n">
-        <v>325.0146255613645</v>
+        <v>325.0061823409892</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26028,28 +26071,28 @@
         <v>0.0454</v>
       </c>
       <c r="I8" t="n">
-        <v>1.086010373155299</v>
+        <v>1.08606846903218</v>
       </c>
       <c r="J8" t="n">
+        <v>571</v>
+      </c>
+      <c r="K8" t="n">
         <v>570</v>
       </c>
-      <c r="K8" t="n">
-        <v>569</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.2299807221637523</v>
+        <v>0.2306936445013518</v>
       </c>
       <c r="M8" t="n">
-        <v>12.19434370278369</v>
+        <v>12.17319881565383</v>
       </c>
       <c r="N8" t="n">
-        <v>228.5864340729495</v>
+        <v>228.1854551593964</v>
       </c>
       <c r="O8" t="n">
-        <v>15.11907517254112</v>
+        <v>15.10580865625526</v>
       </c>
       <c r="P8" t="n">
-        <v>326.5103966790993</v>
+        <v>326.5098198804888</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26087,7 +26130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I571"/>
+  <dimension ref="A1:I572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52708,7 +52751,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>-36.88595759953126,174.4367984852156</t>
+          <t>-36.885977558948674,174.4366899920139</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -52742,6 +52785,53 @@
         </is>
       </c>
       <c r="I571" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>-36.88601309129819,174.43649684771893</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>-36.88500826176572,174.43795139788352</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>-36.884299444354895,174.43779692774507</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>-36.88359868892517,174.43758356678603</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>-36.8829159465724,174.43729255963459</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>-36.88221733259522,174.43706207739726</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>-36.88156090021977,174.4366901579896</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0182/nzd0182.xlsx
+++ b/data/nzd0182/nzd0182.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I572"/>
+  <dimension ref="A1:I575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19208,24 +19208,123 @@
         <v>504.67</v>
       </c>
       <c r="C572" t="n">
-        <v>354.1</v>
+        <v>357.16</v>
       </c>
       <c r="D572" t="n">
-        <v>350.65</v>
+        <v>354.78</v>
       </c>
       <c r="E572" t="n">
-        <v>352.52</v>
+        <v>356.71</v>
       </c>
       <c r="F572" t="n">
-        <v>355.13</v>
+        <v>358.55</v>
       </c>
       <c r="G572" t="n">
-        <v>351.87</v>
+        <v>355.98</v>
       </c>
       <c r="H572" t="n">
         <v>355.34</v>
       </c>
       <c r="I572" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>502.76</v>
+      </c>
+      <c r="C573" t="n">
+        <v>361.81</v>
+      </c>
+      <c r="D573" t="n">
+        <v>360.14</v>
+      </c>
+      <c r="E573" t="n">
+        <v>361.91</v>
+      </c>
+      <c r="F573" t="n">
+        <v>361.92</v>
+      </c>
+      <c r="G573" t="n">
+        <v>359.56</v>
+      </c>
+      <c r="H573" t="n">
+        <v>357.35</v>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>502.76</v>
+      </c>
+      <c r="C574" t="n">
+        <v>363.01</v>
+      </c>
+      <c r="D574" t="n">
+        <v>362.01</v>
+      </c>
+      <c r="E574" t="n">
+        <v>364.07</v>
+      </c>
+      <c r="F574" t="n">
+        <v>361.92</v>
+      </c>
+      <c r="G574" t="n">
+        <v>359.56</v>
+      </c>
+      <c r="H574" t="n">
+        <v>357.35</v>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>496.65</v>
+      </c>
+      <c r="C575" t="n">
+        <v>364.32</v>
+      </c>
+      <c r="D575" t="n">
+        <v>366.11</v>
+      </c>
+      <c r="E575" t="n">
+        <v>364.07</v>
+      </c>
+      <c r="F575" t="n">
+        <v>368.44</v>
+      </c>
+      <c r="G575" t="n">
+        <v>359.56</v>
+      </c>
+      <c r="H575" t="n">
+        <v>361.8</v>
+      </c>
+      <c r="I575" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -19242,7 +19341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B619"/>
+  <dimension ref="A1:B622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25435,6 +25534,36 @@
       </c>
       <c r="B619" t="n">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>
@@ -25603,28 +25732,28 @@
         <v>0.0154</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06847532509849802</v>
+        <v>-0.01997944707394655</v>
       </c>
       <c r="J2" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K2" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000186068757936142</v>
+        <v>1.589681823632727e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>31.61740946308771</v>
+        <v>31.72866002148779</v>
       </c>
       <c r="N2" t="n">
-        <v>1536.508142650632</v>
+        <v>1540.393089046657</v>
       </c>
       <c r="O2" t="n">
-        <v>39.19831810997294</v>
+        <v>39.24784183935031</v>
       </c>
       <c r="P2" t="n">
-        <v>455.0050832511822</v>
+        <v>454.5298227973014</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25681,28 +25810,28 @@
         <v>0.0462</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7085873247826666</v>
+        <v>0.7307162799981893</v>
       </c>
       <c r="J3" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K3" t="n">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2560965886801998</v>
+        <v>0.2648700921929987</v>
       </c>
       <c r="M3" t="n">
-        <v>7.871277472761859</v>
+        <v>7.938940428025147</v>
       </c>
       <c r="N3" t="n">
-        <v>85.17119000443725</v>
+        <v>87.0987496336226</v>
       </c>
       <c r="O3" t="n">
-        <v>9.228823868968204</v>
+        <v>9.332671087830247</v>
       </c>
       <c r="P3" t="n">
-        <v>323.4904332145703</v>
+        <v>323.271121417164</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25759,28 +25888,28 @@
         <v>0.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7459254443505616</v>
+        <v>0.7682070045507595</v>
       </c>
       <c r="J4" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K4" t="n">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2807100763848444</v>
+        <v>0.2893674575449127</v>
       </c>
       <c r="M4" t="n">
-        <v>7.209831202806087</v>
+        <v>7.307796865659935</v>
       </c>
       <c r="N4" t="n">
-        <v>82.75563095988505</v>
+        <v>84.66593960068793</v>
       </c>
       <c r="O4" t="n">
-        <v>9.097012199611752</v>
+        <v>9.201409652911229</v>
       </c>
       <c r="P4" t="n">
-        <v>322.5241937942164</v>
+        <v>322.302270652612</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25837,28 +25966,28 @@
         <v>0.057</v>
       </c>
       <c r="I5" t="n">
-        <v>0.866579947537011</v>
+        <v>0.8818178583224726</v>
       </c>
       <c r="J5" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K5" t="n">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3687937873725903</v>
+        <v>0.3764854725196294</v>
       </c>
       <c r="M5" t="n">
-        <v>6.936634177878799</v>
+        <v>6.977058966095083</v>
       </c>
       <c r="N5" t="n">
-        <v>74.56152749719324</v>
+        <v>75.19168991212987</v>
       </c>
       <c r="O5" t="n">
-        <v>8.634901707442491</v>
+        <v>8.671314197521035</v>
       </c>
       <c r="P5" t="n">
-        <v>326.8544519506864</v>
+        <v>326.7027514024808</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25915,28 +26044,28 @@
         <v>0.0359</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8826869791472011</v>
+        <v>0.8937792063927704</v>
       </c>
       <c r="J6" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K6" t="n">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="L6" t="n">
-        <v>0.275548045913678</v>
+        <v>0.2819613152287155</v>
       </c>
       <c r="M6" t="n">
-        <v>9.003186244191781</v>
+        <v>9.009334474337331</v>
       </c>
       <c r="N6" t="n">
-        <v>118.8325866534211</v>
+        <v>118.7770460701512</v>
       </c>
       <c r="O6" t="n">
-        <v>10.90103603578216</v>
+        <v>10.89848824700707</v>
       </c>
       <c r="P6" t="n">
-        <v>330.9891268206625</v>
+        <v>330.8786856006408</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25993,28 +26122,28 @@
         <v>0.0523</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9235617643485767</v>
+        <v>0.9352054333883076</v>
       </c>
       <c r="J7" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K7" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2157080870044646</v>
+        <v>0.2214246195578293</v>
       </c>
       <c r="M7" t="n">
-        <v>10.7526791942631</v>
+        <v>10.76118775202798</v>
       </c>
       <c r="N7" t="n">
-        <v>180.8198817690829</v>
+        <v>180.4631675351121</v>
       </c>
       <c r="O7" t="n">
-        <v>13.44692833955335</v>
+        <v>13.43365801020378</v>
       </c>
       <c r="P7" t="n">
-        <v>325.0061823409892</v>
+        <v>324.8907480682336</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26071,28 +26200,28 @@
         <v>0.0454</v>
       </c>
       <c r="I8" t="n">
-        <v>1.08606846903218</v>
+        <v>1.089729525588717</v>
       </c>
       <c r="J8" t="n">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K8" t="n">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2306936445013518</v>
+        <v>0.2339114927280698</v>
       </c>
       <c r="M8" t="n">
-        <v>12.17319881565383</v>
+        <v>12.12495891847326</v>
       </c>
       <c r="N8" t="n">
-        <v>228.1854551593964</v>
+        <v>227.0798165808229</v>
       </c>
       <c r="O8" t="n">
-        <v>15.10580865625526</v>
+        <v>15.06916774678758</v>
       </c>
       <c r="P8" t="n">
-        <v>326.5098198804888</v>
+        <v>326.4733490724597</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26130,7 +26259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I572"/>
+  <dimension ref="A1:I575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52803,27 +52932,27 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>-36.88500826176572,174.43795139788352</t>
+          <t>-36.885014418947534,174.4379179317581</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>-36.884299444354895,174.43779692774507</t>
+          <t>-36.88430775449669,174.43775175981517</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>-36.88359868892517,174.43758356678603</t>
+          <t>-36.88360859399272,174.43753820244555</t>
         </is>
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>-36.8829159465724,174.43729255963459</t>
+          <t>-36.8829252548154,174.43725598025844</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>-36.88221733259522,174.43706207739726</t>
+          <t>-36.882230025920755,174.43701875733976</t>
         </is>
       </c>
       <c r="H572" t="inlineStr">
@@ -52832,6 +52961,147 @@
         </is>
       </c>
       <c r="I572" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>-36.88600924834672,174.43651773706006</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>-36.88502377543147,174.43786707636053</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>-36.88431853954646,174.43769313991982</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>-36.88362088665423,174.43748190300838</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>-36.88293442696212,174.43721993565944</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>-36.88224108238145,174.436981023555</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>-36.88156781587552,174.43666931500314</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>-36.88600924834672,174.43651773706006</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>-36.88502619000447,174.43785395238484</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>-36.88432230223432,174.4376726885716</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>-36.88362599282898,174.43745851708277</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>-36.88293442696212,174.43721993565944</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>-36.88224108238145,174.436981023555</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>-36.88156781587552,174.43666931500314</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>-36.88599695490161,174.43658456106317</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>-36.88502882591169,174.43783962537705</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>-36.884330551965625,174.43762784870987</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>-36.88362599282898,174.43745851708277</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>-36.882952172449826,174.43715019949587</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>-36.88224108238145,174.436981023555</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>-36.88158312664293,174.4366231700692</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0182/nzd0182.xlsx
+++ b/data/nzd0182/nzd0182.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I575"/>
+  <dimension ref="A1:I576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19313,18 +19313,51 @@
         <v>366.11</v>
       </c>
       <c r="E575" t="n">
-        <v>364.07</v>
+        <v>370.47</v>
       </c>
       <c r="F575" t="n">
         <v>368.44</v>
       </c>
       <c r="G575" t="n">
-        <v>359.56</v>
+        <v>367.35</v>
       </c>
       <c r="H575" t="n">
         <v>361.8</v>
       </c>
       <c r="I575" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>494.09</v>
+      </c>
+      <c r="C576" t="n">
+        <v>371.13</v>
+      </c>
+      <c r="D576" t="n">
+        <v>378.4</v>
+      </c>
+      <c r="E576" t="n">
+        <v>387.04</v>
+      </c>
+      <c r="F576" t="n">
+        <v>385.23</v>
+      </c>
+      <c r="G576" t="n">
+        <v>383.3</v>
+      </c>
+      <c r="H576" t="n">
+        <v>369.47</v>
+      </c>
+      <c r="I576" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -19341,7 +19374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B622"/>
+  <dimension ref="A1:B623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25564,6 +25597,16 @@
       </c>
       <c r="B622" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>-0.47</v>
       </c>
     </row>
   </sheetData>
@@ -25732,28 +25775,28 @@
         <v>0.0154</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01997944707394655</v>
+        <v>-0.006290547452161425</v>
       </c>
       <c r="J2" t="n">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="K2" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L2" t="n">
-        <v>1.589681823632727e-05</v>
+        <v>1.578920074796208e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>31.72866002148779</v>
+        <v>31.75004207293224</v>
       </c>
       <c r="N2" t="n">
-        <v>1540.393089046657</v>
+        <v>1540.500033286501</v>
       </c>
       <c r="O2" t="n">
-        <v>39.24784183935031</v>
+        <v>39.24920423762119</v>
       </c>
       <c r="P2" t="n">
-        <v>454.5298227973014</v>
+        <v>454.3949341011433</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25810,28 +25853,28 @@
         <v>0.0462</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7307162799981893</v>
+        <v>0.7403708629117738</v>
       </c>
       <c r="J3" t="n">
+        <v>575</v>
+      </c>
+      <c r="K3" t="n">
         <v>574</v>
       </c>
-      <c r="K3" t="n">
-        <v>573</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.2648700921929987</v>
+        <v>0.2676370755769678</v>
       </c>
       <c r="M3" t="n">
-        <v>7.938940428025147</v>
+        <v>7.972860607363934</v>
       </c>
       <c r="N3" t="n">
-        <v>87.0987496336226</v>
+        <v>88.34906108653757</v>
       </c>
       <c r="O3" t="n">
-        <v>9.332671087830247</v>
+        <v>9.399418124891433</v>
       </c>
       <c r="P3" t="n">
-        <v>323.271121417164</v>
+        <v>323.174953738081</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25888,28 +25931,28 @@
         <v>0.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7682070045507595</v>
+        <v>0.7803764423248395</v>
       </c>
       <c r="J4" t="n">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="K4" t="n">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2893674575449127</v>
+        <v>0.29133344545615</v>
       </c>
       <c r="M4" t="n">
-        <v>7.307796865659935</v>
+        <v>7.36962130518947</v>
       </c>
       <c r="N4" t="n">
-        <v>84.66593960068793</v>
+        <v>86.72790127520287</v>
       </c>
       <c r="O4" t="n">
-        <v>9.201409652911229</v>
+        <v>9.312781607833552</v>
       </c>
       <c r="P4" t="n">
-        <v>322.302270652612</v>
+        <v>322.1804533567433</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25966,28 +26009,28 @@
         <v>0.057</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8818178583224726</v>
+        <v>0.8965684583537731</v>
       </c>
       <c r="J5" t="n">
+        <v>575</v>
+      </c>
+      <c r="K5" t="n">
         <v>574</v>
       </c>
-      <c r="K5" t="n">
-        <v>573</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.3764854725196294</v>
+        <v>0.3767810017346629</v>
       </c>
       <c r="M5" t="n">
-        <v>6.977058966095083</v>
+        <v>7.039615435393659</v>
       </c>
       <c r="N5" t="n">
-        <v>75.19168991212987</v>
+        <v>77.79953900822878</v>
       </c>
       <c r="O5" t="n">
-        <v>8.671314197521035</v>
+        <v>8.82040469639737</v>
       </c>
       <c r="P5" t="n">
-        <v>326.7027514024808</v>
+        <v>326.5552299237133</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26044,28 +26087,28 @@
         <v>0.0359</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8937792063927704</v>
+        <v>0.9042132402799815</v>
       </c>
       <c r="J6" t="n">
+        <v>575</v>
+      </c>
+      <c r="K6" t="n">
         <v>574</v>
       </c>
-      <c r="K6" t="n">
-        <v>573</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.2819613152287155</v>
+        <v>0.2847111152672028</v>
       </c>
       <c r="M6" t="n">
-        <v>9.009334474337331</v>
+        <v>9.04335089494038</v>
       </c>
       <c r="N6" t="n">
-        <v>118.7770460701512</v>
+        <v>120.1924538364085</v>
       </c>
       <c r="O6" t="n">
-        <v>10.89848824700707</v>
+        <v>10.96323190653233</v>
       </c>
       <c r="P6" t="n">
-        <v>330.8786856006408</v>
+        <v>330.7742739362225</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26122,28 +26165,28 @@
         <v>0.0523</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9352054333883076</v>
+        <v>0.9492205018176452</v>
       </c>
       <c r="J7" t="n">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="K7" t="n">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2214246195578293</v>
+        <v>0.2250463608622195</v>
       </c>
       <c r="M7" t="n">
-        <v>10.76118775202798</v>
+        <v>10.82038424146236</v>
       </c>
       <c r="N7" t="n">
-        <v>180.4631675351121</v>
+        <v>182.4651917436301</v>
       </c>
       <c r="O7" t="n">
-        <v>13.43365801020378</v>
+        <v>13.50796771330277</v>
       </c>
       <c r="P7" t="n">
-        <v>324.8907480682336</v>
+        <v>324.7511695400802</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26200,28 +26243,28 @@
         <v>0.0454</v>
       </c>
       <c r="I8" t="n">
-        <v>1.089729525588717</v>
+        <v>1.094517667794746</v>
       </c>
       <c r="J8" t="n">
+        <v>575</v>
+      </c>
+      <c r="K8" t="n">
         <v>574</v>
       </c>
-      <c r="K8" t="n">
-        <v>573</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.2339114927280698</v>
+        <v>0.2359211379083296</v>
       </c>
       <c r="M8" t="n">
-        <v>12.12495891847326</v>
+        <v>12.12398425102124</v>
       </c>
       <c r="N8" t="n">
-        <v>227.0798165808229</v>
+        <v>227.0258485594246</v>
       </c>
       <c r="O8" t="n">
-        <v>15.06916774678758</v>
+        <v>15.06737696347392</v>
       </c>
       <c r="P8" t="n">
-        <v>326.4733490724597</v>
+        <v>326.4254349193519</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26259,7 +26302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I575"/>
+  <dimension ref="A1:I576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53083,7 +53126,7 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>-36.88362599282898,174.43745851708277</t>
+          <t>-36.88364112220896,174.43738922543216</t>
         </is>
       </c>
       <c r="F575" t="inlineStr">
@@ -53093,7 +53136,7 @@
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>-36.88224108238145,174.436981023555</t>
+          <t>-36.88226514095216,174.43689891564372</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
@@ -53102,6 +53145,53 @@
         </is>
       </c>
       <c r="I575" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>-36.88599180411815,174.43661255932943</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>-36.885042528577465,174.43776514679305</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>-36.884355280937946,174.4374934384291</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>-36.883680292934066,174.43720982488517</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>-36.882997869616915,174.43697061802473</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>-36.882314400624615,174.43673079979294</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>-36.881609516171544,174.43654363482395</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0182/nzd0182.xlsx
+++ b/data/nzd0182/nzd0182.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I576"/>
+  <dimension ref="A1:I577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19360,6 +19360,39 @@
       <c r="I576" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-25 22:12:21+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>488.02</v>
+      </c>
+      <c r="C577" t="n">
+        <v>372.06</v>
+      </c>
+      <c r="D577" t="n">
+        <v>379.46</v>
+      </c>
+      <c r="E577" t="n">
+        <v>389.3</v>
+      </c>
+      <c r="F577" t="n">
+        <v>387.25</v>
+      </c>
+      <c r="G577" t="n">
+        <v>388.34</v>
+      </c>
+      <c r="H577" t="n">
+        <v>375.52</v>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -19374,7 +19407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B623"/>
+  <dimension ref="A1:B624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25607,6 +25640,16 @@
       </c>
       <c r="B623" t="n">
         <v>-0.47</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-02-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>-0.67</v>
       </c>
     </row>
   </sheetData>
@@ -25775,28 +25818,28 @@
         <v>0.0154</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.006290547452161425</v>
+        <v>0.005226224527544816</v>
       </c>
       <c r="J2" t="n">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="K2" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L2" t="n">
-        <v>1.578920074796208e-06</v>
+        <v>1.092539475666676e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>31.75004207293224</v>
+        <v>31.75836000666761</v>
       </c>
       <c r="N2" t="n">
-        <v>1540.500033286501</v>
+        <v>1539.746046793892</v>
       </c>
       <c r="O2" t="n">
-        <v>39.24920423762119</v>
+        <v>39.23959794383592</v>
       </c>
       <c r="P2" t="n">
-        <v>454.3949341011433</v>
+        <v>454.2812204427485</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25853,28 +25896,28 @@
         <v>0.0462</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7403708629117738</v>
+        <v>0.7502533937512154</v>
       </c>
       <c r="J3" t="n">
+        <v>576</v>
+      </c>
+      <c r="K3" t="n">
         <v>575</v>
       </c>
-      <c r="K3" t="n">
-        <v>574</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.2676370755769678</v>
+        <v>0.2703640082919261</v>
       </c>
       <c r="M3" t="n">
-        <v>7.972860607363934</v>
+        <v>8.007863667044434</v>
       </c>
       <c r="N3" t="n">
-        <v>88.34906108653757</v>
+        <v>89.66799889378716</v>
       </c>
       <c r="O3" t="n">
-        <v>9.399418124891433</v>
+        <v>9.46931881889015</v>
       </c>
       <c r="P3" t="n">
-        <v>323.174953738081</v>
+        <v>323.0763345682757</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25931,28 +25974,28 @@
         <v>0.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7803764423248395</v>
+        <v>0.7928035631377569</v>
       </c>
       <c r="J4" t="n">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="K4" t="n">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L4" t="n">
-        <v>0.29133344545615</v>
+        <v>0.2932330036386323</v>
       </c>
       <c r="M4" t="n">
-        <v>7.36962130518947</v>
+        <v>7.432908863297139</v>
       </c>
       <c r="N4" t="n">
-        <v>86.72790127520287</v>
+        <v>88.88666229400344</v>
       </c>
       <c r="O4" t="n">
-        <v>9.312781607833552</v>
+        <v>9.42797233205547</v>
       </c>
       <c r="P4" t="n">
-        <v>322.1804533567433</v>
+        <v>322.0558291612141</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26009,28 +26052,28 @@
         <v>0.057</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8965684583537731</v>
+        <v>0.9098014082524555</v>
       </c>
       <c r="J5" t="n">
+        <v>576</v>
+      </c>
+      <c r="K5" t="n">
         <v>575</v>
       </c>
-      <c r="K5" t="n">
-        <v>574</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.3767810017346629</v>
+        <v>0.3768034345302805</v>
       </c>
       <c r="M5" t="n">
-        <v>7.039615435393659</v>
+        <v>7.094210239826262</v>
       </c>
       <c r="N5" t="n">
-        <v>77.79953900822878</v>
+        <v>80.2800155371941</v>
       </c>
       <c r="O5" t="n">
-        <v>8.82040469639737</v>
+        <v>8.959911580880366</v>
       </c>
       <c r="P5" t="n">
-        <v>326.5552299237133</v>
+        <v>326.4225683486935</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26087,28 +26130,28 @@
         <v>0.0359</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9042132402799815</v>
+        <v>0.9152424457924987</v>
       </c>
       <c r="J6" t="n">
+        <v>576</v>
+      </c>
+      <c r="K6" t="n">
         <v>575</v>
       </c>
-      <c r="K6" t="n">
-        <v>574</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.2847111152672028</v>
+        <v>0.2873935311386907</v>
       </c>
       <c r="M6" t="n">
-        <v>9.04335089494038</v>
+        <v>9.080498941818302</v>
       </c>
       <c r="N6" t="n">
-        <v>120.1924538364085</v>
+        <v>121.8005131095637</v>
       </c>
       <c r="O6" t="n">
-        <v>10.96323190653233</v>
+        <v>11.03632697547348</v>
       </c>
       <c r="P6" t="n">
-        <v>330.7742739362225</v>
+        <v>330.6637051072228</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26165,28 +26208,28 @@
         <v>0.0523</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9492205018176452</v>
+        <v>0.9622050844513031</v>
       </c>
       <c r="J7" t="n">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="K7" t="n">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2250463608622195</v>
+        <v>0.2280693178765463</v>
       </c>
       <c r="M7" t="n">
-        <v>10.82038424146236</v>
+        <v>10.87347020613405</v>
       </c>
       <c r="N7" t="n">
-        <v>182.4651917436301</v>
+        <v>184.6851684360566</v>
       </c>
       <c r="O7" t="n">
-        <v>13.50796771330277</v>
+        <v>13.58989214217893</v>
       </c>
       <c r="P7" t="n">
-        <v>324.7511695400802</v>
+        <v>324.6215208279775</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26243,28 +26286,28 @@
         <v>0.0454</v>
       </c>
       <c r="I8" t="n">
-        <v>1.094517667794746</v>
+        <v>1.101311750958713</v>
       </c>
       <c r="J8" t="n">
+        <v>576</v>
+      </c>
+      <c r="K8" t="n">
         <v>575</v>
       </c>
-      <c r="K8" t="n">
-        <v>574</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.2359211379083296</v>
+        <v>0.2383191468753987</v>
       </c>
       <c r="M8" t="n">
-        <v>12.12398425102124</v>
+        <v>12.13173951026209</v>
       </c>
       <c r="N8" t="n">
-        <v>227.0258485594246</v>
+        <v>227.3205453476453</v>
       </c>
       <c r="O8" t="n">
-        <v>15.06737696347392</v>
+        <v>15.07715309160338</v>
       </c>
       <c r="P8" t="n">
-        <v>326.4254349193519</v>
+        <v>326.3573235926826</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26302,7 +26345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I576"/>
+  <dimension ref="A1:I577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53197,6 +53240,53 @@
         </is>
       </c>
     </row>
+    <row r="577">
+      <c r="A577" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-25 22:12:21+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>-36.8859795911016,174.4366789458277</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>-36.88504439986305,174.43775497570672</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>-36.88435741377962,174.43748184567482</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>-36.88368563545039,174.43718535623805</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>-36.88300336741174,174.43694901261534</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>-36.88232996601486,174.4366776772458</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>-36.88163033186462,174.4364808983783</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0182/nzd0182.xlsx
+++ b/data/nzd0182/nzd0182.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I577"/>
+  <dimension ref="A1:I578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19393,6 +19393,39 @@
       <c r="I577" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>485.99</v>
+      </c>
+      <c r="C578" t="n">
+        <v>371.75</v>
+      </c>
+      <c r="D578" t="n">
+        <v>379.3</v>
+      </c>
+      <c r="E578" t="n">
+        <v>389.56</v>
+      </c>
+      <c r="F578" t="n">
+        <v>388.02</v>
+      </c>
+      <c r="G578" t="n">
+        <v>389.01</v>
+      </c>
+      <c r="H578" t="n">
+        <v>377.61</v>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -19407,7 +19440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B624"/>
+  <dimension ref="A1:B625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25650,6 +25683,16 @@
       </c>
       <c r="B624" t="n">
         <v>-0.67</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>-0.39</v>
       </c>
     </row>
   </sheetData>
@@ -25818,28 +25861,28 @@
         <v>0.0154</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005226224527544816</v>
+        <v>0.01592654726672444</v>
       </c>
       <c r="J2" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="K2" t="n">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L2" t="n">
-        <v>1.092539475666676e-06</v>
+        <v>1.017285138515955e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>31.75836000666761</v>
+        <v>31.76186096115357</v>
       </c>
       <c r="N2" t="n">
-        <v>1539.746046793892</v>
+        <v>1538.726204401495</v>
       </c>
       <c r="O2" t="n">
-        <v>39.23959794383592</v>
+        <v>39.22660072452742</v>
       </c>
       <c r="P2" t="n">
-        <v>454.2812204427485</v>
+        <v>454.1755539949919</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25896,28 +25939,28 @@
         <v>0.0462</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7502533937512154</v>
+        <v>0.7599222026992928</v>
       </c>
       <c r="J3" t="n">
+        <v>577</v>
+      </c>
+      <c r="K3" t="n">
         <v>576</v>
       </c>
-      <c r="K3" t="n">
-        <v>575</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.2703640082919261</v>
+        <v>0.273079994154061</v>
       </c>
       <c r="M3" t="n">
-        <v>8.007863667044434</v>
+        <v>8.041782290295362</v>
       </c>
       <c r="N3" t="n">
-        <v>89.66799889378716</v>
+        <v>90.93472672029048</v>
       </c>
       <c r="O3" t="n">
-        <v>9.46931881889015</v>
+        <v>9.535970150975226</v>
       </c>
       <c r="P3" t="n">
-        <v>323.0763345682757</v>
+        <v>322.9798363359077</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25974,28 +26017,28 @@
         <v>0.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7928035631377569</v>
+        <v>0.8050392031022486</v>
       </c>
       <c r="J4" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="K4" t="n">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2932330036386323</v>
+        <v>0.2951791589757856</v>
       </c>
       <c r="M4" t="n">
-        <v>7.432908863297139</v>
+        <v>7.496567752954152</v>
       </c>
       <c r="N4" t="n">
-        <v>88.88666229400344</v>
+        <v>90.99169883714637</v>
       </c>
       <c r="O4" t="n">
-        <v>9.42797233205547</v>
+        <v>9.538956905089066</v>
       </c>
       <c r="P4" t="n">
-        <v>322.0558291612141</v>
+        <v>321.9331102548798</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26052,28 +26095,28 @@
         <v>0.057</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9098014082524555</v>
+        <v>0.9229739205861229</v>
       </c>
       <c r="J5" t="n">
+        <v>577</v>
+      </c>
+      <c r="K5" t="n">
         <v>576</v>
       </c>
-      <c r="K5" t="n">
-        <v>575</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.3768034345302805</v>
+        <v>0.3769265905738689</v>
       </c>
       <c r="M5" t="n">
-        <v>7.094210239826262</v>
+        <v>7.149407436901271</v>
       </c>
       <c r="N5" t="n">
-        <v>80.2800155371941</v>
+        <v>82.7562038519979</v>
       </c>
       <c r="O5" t="n">
-        <v>8.959911580880366</v>
+        <v>9.097043687484296</v>
       </c>
       <c r="P5" t="n">
-        <v>326.4225683486935</v>
+        <v>326.2904966021823</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26130,28 +26173,28 @@
         <v>0.0359</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9152424457924987</v>
+        <v>0.9264117009857561</v>
       </c>
       <c r="J6" t="n">
+        <v>577</v>
+      </c>
+      <c r="K6" t="n">
         <v>576</v>
       </c>
-      <c r="K6" t="n">
-        <v>575</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.2873935311386907</v>
+        <v>0.290022637857584</v>
       </c>
       <c r="M6" t="n">
-        <v>9.080498941818302</v>
+        <v>9.118966934425757</v>
       </c>
       <c r="N6" t="n">
-        <v>121.8005131095637</v>
+        <v>123.4695673252369</v>
       </c>
       <c r="O6" t="n">
-        <v>11.03632697547348</v>
+        <v>11.1116860703152</v>
       </c>
       <c r="P6" t="n">
-        <v>330.6637051072228</v>
+        <v>330.5517186460804</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26208,28 +26251,28 @@
         <v>0.0523</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9622050844513031</v>
+        <v>0.9752697864185902</v>
       </c>
       <c r="J7" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="K7" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2280693178765463</v>
+        <v>0.231057769998684</v>
       </c>
       <c r="M7" t="n">
-        <v>10.87347020613405</v>
+        <v>10.92733296909437</v>
       </c>
       <c r="N7" t="n">
-        <v>184.6851684360566</v>
+        <v>186.9566049637366</v>
       </c>
       <c r="O7" t="n">
-        <v>13.58989214217893</v>
+        <v>13.67320755944766</v>
       </c>
       <c r="P7" t="n">
-        <v>324.6215208279775</v>
+        <v>324.4910561993482</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26286,28 +26329,28 @@
         <v>0.0454</v>
       </c>
       <c r="I8" t="n">
-        <v>1.101311750958713</v>
+        <v>1.108737189946118</v>
       </c>
       <c r="J8" t="n">
+        <v>577</v>
+      </c>
+      <c r="K8" t="n">
         <v>576</v>
       </c>
-      <c r="K8" t="n">
-        <v>575</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.2383191468753987</v>
+        <v>0.2408102796176114</v>
       </c>
       <c r="M8" t="n">
-        <v>12.13173951026209</v>
+        <v>12.14225138785537</v>
       </c>
       <c r="N8" t="n">
-        <v>227.3205453476453</v>
+        <v>227.7570279833506</v>
       </c>
       <c r="O8" t="n">
-        <v>15.07715309160338</v>
+        <v>15.09162111846672</v>
       </c>
       <c r="P8" t="n">
-        <v>326.3573235926826</v>
+        <v>326.2828738088572</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26345,7 +26388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I577"/>
+  <dimension ref="A1:I578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53287,6 +53330,53 @@
         </is>
       </c>
     </row>
+    <row r="578">
+      <c r="A578" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>-36.88597550667438,174.43670114756765</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>-36.885043776101284,174.4377583660689</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>-36.884357091841316,174.43748359552455</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>-36.883686250075854,174.43718254126074</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>-36.8830054631048,174.43694077688914</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>-36.882332035221715,174.4366706153182</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>-36.88163752273286,174.43645922577986</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0182/nzd0182.xlsx
+++ b/data/nzd0182/nzd0182.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I578"/>
+  <dimension ref="A1:I580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19424,6 +19424,72 @@
         <v>377.61</v>
       </c>
       <c r="I578" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>483.49</v>
+      </c>
+      <c r="C579" t="n">
+        <v>373.73</v>
+      </c>
+      <c r="D579" t="n">
+        <v>382.52</v>
+      </c>
+      <c r="E579" t="n">
+        <v>394.1</v>
+      </c>
+      <c r="F579" t="n">
+        <v>394.29</v>
+      </c>
+      <c r="G579" t="n">
+        <v>395.65</v>
+      </c>
+      <c r="H579" t="n">
+        <v>385.58</v>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>483.49</v>
+      </c>
+      <c r="C580" t="n">
+        <v>378.53</v>
+      </c>
+      <c r="D580" t="n">
+        <v>385.88</v>
+      </c>
+      <c r="E580" t="n">
+        <v>396.99</v>
+      </c>
+      <c r="F580" t="n">
+        <v>397.67</v>
+      </c>
+      <c r="G580" t="n">
+        <v>399.13</v>
+      </c>
+      <c r="H580" t="n">
+        <v>391.02</v>
+      </c>
+      <c r="I580" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -19440,7 +19506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B625"/>
+  <dimension ref="A1:B627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25693,6 +25759,26 @@
       </c>
       <c r="B625" t="n">
         <v>-0.39</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>0.91</v>
       </c>
     </row>
   </sheetData>
@@ -25861,28 +25947,28 @@
         <v>0.0154</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01592654726672444</v>
+        <v>0.03545538853293822</v>
       </c>
       <c r="J2" t="n">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="K2" t="n">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="L2" t="n">
-        <v>1.017285138515955e-05</v>
+        <v>5.070212411595332e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>31.76186096115357</v>
+        <v>31.75703934474289</v>
       </c>
       <c r="N2" t="n">
-        <v>1538.726204401495</v>
+        <v>1536.083525531023</v>
       </c>
       <c r="O2" t="n">
-        <v>39.22660072452742</v>
+        <v>39.19290146864637</v>
       </c>
       <c r="P2" t="n">
-        <v>454.1755539949919</v>
+        <v>453.9817881818148</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25939,28 +26025,28 @@
         <v>0.0462</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7599222026992928</v>
+        <v>0.7819968822272406</v>
       </c>
       <c r="J3" t="n">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="K3" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L3" t="n">
-        <v>0.273079994154061</v>
+        <v>0.2780559882229922</v>
       </c>
       <c r="M3" t="n">
-        <v>8.041782290295362</v>
+        <v>8.124522100794824</v>
       </c>
       <c r="N3" t="n">
-        <v>90.93472672029048</v>
+        <v>94.33239747544289</v>
       </c>
       <c r="O3" t="n">
-        <v>9.535970150975226</v>
+        <v>9.712486678263343</v>
       </c>
       <c r="P3" t="n">
-        <v>322.9798363359077</v>
+        <v>322.758543240722</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26017,28 +26103,28 @@
         <v>0.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8050392031022486</v>
+        <v>0.8325611037459942</v>
       </c>
       <c r="J4" t="n">
+        <v>579</v>
+      </c>
+      <c r="K4" t="n">
         <v>577</v>
       </c>
-      <c r="K4" t="n">
-        <v>575</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.2951791589757856</v>
+        <v>0.29810892193004</v>
       </c>
       <c r="M4" t="n">
-        <v>7.496567752954152</v>
+        <v>7.642160357967996</v>
       </c>
       <c r="N4" t="n">
-        <v>90.99169883714637</v>
+        <v>96.38084850104642</v>
       </c>
       <c r="O4" t="n">
-        <v>9.538956905089066</v>
+        <v>9.817374827368385</v>
       </c>
       <c r="P4" t="n">
-        <v>321.9331102548798</v>
+        <v>321.6558680497062</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26095,28 +26181,28 @@
         <v>0.057</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9229739205861229</v>
+        <v>0.9530826298621496</v>
       </c>
       <c r="J5" t="n">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="K5" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3769265905738689</v>
+        <v>0.3751980810431769</v>
       </c>
       <c r="M5" t="n">
-        <v>7.149407436901271</v>
+        <v>7.281243661599443</v>
       </c>
       <c r="N5" t="n">
-        <v>82.7562038519979</v>
+        <v>89.28454213337308</v>
       </c>
       <c r="O5" t="n">
-        <v>9.097043687484296</v>
+        <v>9.449049800555244</v>
       </c>
       <c r="P5" t="n">
-        <v>326.2904966021823</v>
+        <v>325.9873032106526</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26173,28 +26259,28 @@
         <v>0.0359</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9264117009857561</v>
+        <v>0.9538731471845718</v>
       </c>
       <c r="J6" t="n">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="K6" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L6" t="n">
-        <v>0.290022637857584</v>
+        <v>0.2944032946481061</v>
       </c>
       <c r="M6" t="n">
-        <v>9.118966934425757</v>
+        <v>9.221112864288006</v>
       </c>
       <c r="N6" t="n">
-        <v>123.4695673252369</v>
+        <v>128.7148174194113</v>
       </c>
       <c r="O6" t="n">
-        <v>11.1116860703152</v>
+        <v>11.34525528224955</v>
       </c>
       <c r="P6" t="n">
-        <v>330.5517186460804</v>
+        <v>330.2751792878092</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26251,28 +26337,28 @@
         <v>0.0523</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9752697864185902</v>
+        <v>1.006754088531355</v>
       </c>
       <c r="J7" t="n">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="K7" t="n">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="L7" t="n">
-        <v>0.231057769998684</v>
+        <v>0.2367648459381279</v>
       </c>
       <c r="M7" t="n">
-        <v>10.92733296909437</v>
+        <v>11.06580161833889</v>
       </c>
       <c r="N7" t="n">
-        <v>186.9566049637366</v>
+        <v>193.8185761164492</v>
       </c>
       <c r="O7" t="n">
-        <v>13.67320755944766</v>
+        <v>13.92187401596672</v>
       </c>
       <c r="P7" t="n">
-        <v>324.4910561993482</v>
+        <v>324.1752757687332</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26329,28 +26415,28 @@
         <v>0.0454</v>
       </c>
       <c r="I8" t="n">
-        <v>1.108737189946118</v>
+        <v>1.130609701293626</v>
       </c>
       <c r="J8" t="n">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="K8" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2408102796176114</v>
+        <v>0.2465399397075193</v>
       </c>
       <c r="M8" t="n">
-        <v>12.14225138785537</v>
+        <v>12.19333015698855</v>
       </c>
       <c r="N8" t="n">
-        <v>227.7570279833506</v>
+        <v>230.5853898542398</v>
       </c>
       <c r="O8" t="n">
-        <v>15.09162111846672</v>
+        <v>15.18503835537598</v>
       </c>
       <c r="P8" t="n">
-        <v>326.2828738088572</v>
+        <v>326.0626015586317</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26388,7 +26474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I578"/>
+  <dimension ref="A1:I580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53377,6 +53463,100 @@
         </is>
       </c>
     </row>
+    <row r="579">
+      <c r="A579" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>-36.88597047658595,174.43672848960844</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>-36.88504776012639,174.43773671149663</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>-36.884363570844585,174.43744837979537</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>-36.88369698237125,174.4371333874182</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>-36.88302252801299,174.43687371452984</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>-36.88235254196597,174.4366006284325</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>-36.8816649443336,174.43637657951683</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>-36.88597047658595,174.43672848960844</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>-36.885057418352865,174.43768421555393</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>-36.88437033153264,174.43741163294084</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>-36.88370381415235,174.43710209785021</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>-36.88303172726225,174.4368375628783</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>-36.88236328946035,174.4365639485432</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>-36.88168366117805,174.4363201684819</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0182/nzd0182.xlsx
+++ b/data/nzd0182/nzd0182.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I580"/>
+  <dimension ref="A1:I586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19490,6 +19490,204 @@
         <v>391.02</v>
       </c>
       <c r="I580" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>481.96</v>
+      </c>
+      <c r="C581" t="n">
+        <v>379.03</v>
+      </c>
+      <c r="D581" t="n">
+        <v>386.43</v>
+      </c>
+      <c r="E581" t="n">
+        <v>396.99</v>
+      </c>
+      <c r="F581" t="n">
+        <v>397.67</v>
+      </c>
+      <c r="G581" t="n">
+        <v>399.13</v>
+      </c>
+      <c r="H581" t="n">
+        <v>391.02</v>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>472.11</v>
+      </c>
+      <c r="C582" t="n">
+        <v>375.8</v>
+      </c>
+      <c r="D582" t="n">
+        <v>383.73</v>
+      </c>
+      <c r="E582" t="n">
+        <v>393.26</v>
+      </c>
+      <c r="F582" t="n">
+        <v>394.17</v>
+      </c>
+      <c r="G582" t="n">
+        <v>392.92</v>
+      </c>
+      <c r="H582" t="n">
+        <v>388.59</v>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>468.54</v>
+      </c>
+      <c r="C583" t="n">
+        <v>375.26</v>
+      </c>
+      <c r="D583" t="n">
+        <v>382.78</v>
+      </c>
+      <c r="E583" t="n">
+        <v>392.35</v>
+      </c>
+      <c r="F583" t="n">
+        <v>393.01</v>
+      </c>
+      <c r="G583" t="n">
+        <v>390.08</v>
+      </c>
+      <c r="H583" t="n">
+        <v>387.75</v>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>467.39</v>
+      </c>
+      <c r="C584" t="n">
+        <v>372.81</v>
+      </c>
+      <c r="D584" t="n">
+        <v>380.86</v>
+      </c>
+      <c r="E584" t="n">
+        <v>390.86</v>
+      </c>
+      <c r="F584" t="n">
+        <v>391.52</v>
+      </c>
+      <c r="G584" t="n">
+        <v>390.36</v>
+      </c>
+      <c r="H584" t="n">
+        <v>388.15</v>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>465.78</v>
+      </c>
+      <c r="C585" t="n">
+        <v>372.03</v>
+      </c>
+      <c r="D585" t="n">
+        <v>379.74</v>
+      </c>
+      <c r="E585" t="n">
+        <v>389.68</v>
+      </c>
+      <c r="F585" t="n">
+        <v>391.47</v>
+      </c>
+      <c r="G585" t="n">
+        <v>389.72</v>
+      </c>
+      <c r="H585" t="n">
+        <v>388.73</v>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>464.87</v>
+      </c>
+      <c r="C586" t="n">
+        <v>372.02</v>
+      </c>
+      <c r="D586" t="n">
+        <v>379.2</v>
+      </c>
+      <c r="E586" t="n">
+        <v>389</v>
+      </c>
+      <c r="F586" t="n">
+        <v>391.69</v>
+      </c>
+      <c r="G586" t="n">
+        <v>389.76</v>
+      </c>
+      <c r="H586" t="n">
+        <v>389.72</v>
+      </c>
+      <c r="I586" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -19506,7 +19704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B627"/>
+  <dimension ref="A1:B633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25779,6 +25977,66 @@
       </c>
       <c r="B627" t="n">
         <v>0.91</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>
@@ -25947,28 +26205,28 @@
         <v>0.0154</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03545538853293822</v>
+        <v>0.06541900454545291</v>
       </c>
       <c r="J2" t="n">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="K2" t="n">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="L2" t="n">
-        <v>5.070212411595332e-05</v>
+        <v>0.0001762409786111307</v>
       </c>
       <c r="M2" t="n">
-        <v>31.75703934474289</v>
+        <v>31.57900171589796</v>
       </c>
       <c r="N2" t="n">
-        <v>1536.083525531023</v>
+        <v>1522.016676844012</v>
       </c>
       <c r="O2" t="n">
-        <v>39.19290146864637</v>
+        <v>39.01303214111935</v>
       </c>
       <c r="P2" t="n">
-        <v>453.9817881818148</v>
+        <v>453.6832979652541</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26025,28 +26283,28 @@
         <v>0.0462</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7819968822272406</v>
+        <v>0.8424410365465288</v>
       </c>
       <c r="J3" t="n">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="K3" t="n">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2780559882229922</v>
+        <v>0.2934305254808601</v>
       </c>
       <c r="M3" t="n">
-        <v>8.124522100794824</v>
+        <v>8.363161652028003</v>
       </c>
       <c r="N3" t="n">
-        <v>94.33239747544289</v>
+        <v>102.8388336919588</v>
       </c>
       <c r="O3" t="n">
-        <v>9.712486678263343</v>
+        <v>10.14094836255263</v>
       </c>
       <c r="P3" t="n">
-        <v>322.758543240722</v>
+        <v>322.150282998593</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26103,28 +26361,28 @@
         <v>0.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8325611037459942</v>
+        <v>0.9078710171888338</v>
       </c>
       <c r="J4" t="n">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="K4" t="n">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="L4" t="n">
-        <v>0.29810892193004</v>
+        <v>0.3096020624344875</v>
       </c>
       <c r="M4" t="n">
-        <v>7.642160357967996</v>
+        <v>8.050485894447283</v>
       </c>
       <c r="N4" t="n">
-        <v>96.38084850104642</v>
+        <v>109.9434317061451</v>
       </c>
       <c r="O4" t="n">
-        <v>9.817374827368385</v>
+        <v>10.48539134730531</v>
       </c>
       <c r="P4" t="n">
-        <v>321.6558680497062</v>
+        <v>320.8942901905784</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26181,28 +26439,28 @@
         <v>0.057</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9530826298621496</v>
+        <v>1.032990760395662</v>
       </c>
       <c r="J5" t="n">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="K5" t="n">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3751980810431769</v>
+        <v>0.3785496422868693</v>
       </c>
       <c r="M5" t="n">
-        <v>7.281243661599443</v>
+        <v>7.640214505323305</v>
       </c>
       <c r="N5" t="n">
-        <v>89.28454213337308</v>
+        <v>104.7336995238627</v>
       </c>
       <c r="O5" t="n">
-        <v>9.449049800555244</v>
+        <v>10.2339483838772</v>
       </c>
       <c r="P5" t="n">
-        <v>325.9873032106526</v>
+        <v>325.1795056056022</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26259,28 +26517,28 @@
         <v>0.0359</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9538731471845718</v>
+        <v>1.027707846655009</v>
       </c>
       <c r="J6" t="n">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="K6" t="n">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2944032946481061</v>
+        <v>0.3087861512498975</v>
       </c>
       <c r="M6" t="n">
-        <v>9.221112864288006</v>
+        <v>9.492556176956191</v>
       </c>
       <c r="N6" t="n">
-        <v>128.7148174194113</v>
+        <v>141.3526417699485</v>
       </c>
       <c r="O6" t="n">
-        <v>11.34525528224955</v>
+        <v>11.88918171153711</v>
       </c>
       <c r="P6" t="n">
-        <v>330.2751792878092</v>
+        <v>329.5287695968746</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26337,28 +26595,28 @@
         <v>0.0523</v>
       </c>
       <c r="I7" t="n">
-        <v>1.006754088531355</v>
+        <v>1.086985574208206</v>
       </c>
       <c r="J7" t="n">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="K7" t="n">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2367648459381279</v>
+        <v>0.2540142856688444</v>
       </c>
       <c r="M7" t="n">
-        <v>11.06580161833889</v>
+        <v>11.40337302390657</v>
       </c>
       <c r="N7" t="n">
-        <v>193.8185761164492</v>
+        <v>208.4921908371671</v>
       </c>
       <c r="O7" t="n">
-        <v>13.92187401596672</v>
+        <v>14.43925866646786</v>
       </c>
       <c r="P7" t="n">
-        <v>324.1752757687332</v>
+        <v>323.3674409007422</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26415,28 +26673,28 @@
         <v>0.0454</v>
       </c>
       <c r="I8" t="n">
-        <v>1.130609701293626</v>
+        <v>1.195006714421148</v>
       </c>
       <c r="J8" t="n">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="K8" t="n">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2465399397075193</v>
+        <v>0.2633635402243283</v>
       </c>
       <c r="M8" t="n">
-        <v>12.19333015698855</v>
+        <v>12.34474092112029</v>
       </c>
       <c r="N8" t="n">
-        <v>230.5853898542398</v>
+        <v>238.8076407708864</v>
       </c>
       <c r="O8" t="n">
-        <v>15.18503835537598</v>
+        <v>15.45340223934155</v>
       </c>
       <c r="P8" t="n">
-        <v>326.0626015586317</v>
+        <v>325.4115684587705</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26474,7 +26732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I580"/>
+  <dimension ref="A1:I586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53557,6 +53815,288 @@
         </is>
       </c>
     </row>
+    <row r="581">
+      <c r="A581" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>-36.88596739816877,174.43674522293554</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>-36.885058424416805,174.43767874722576</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>-36.884371438191806,174.43740561783005</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>-36.88370381415235,174.43710209785021</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>-36.88303172726225,174.4368375628783</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>-36.88236328946035,174.4365639485432</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>-36.88168366117805,174.4363201684819</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>-36.885947579544855,174.43685295053027</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>-36.88505192523938,174.43771407262304</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>-36.884366005498414,174.4374351465539</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>-36.88369499666171,174.43714248196287</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>-36.883022201412224,174.43687499802024</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>-36.88234411073417,174.43662940316577</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>-36.88167530053203,174.43634536679696</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:29+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>-36.885940396527374,174.43689199493335</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>-36.88505083868857,174.4377199784164</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>-36.88436409399347,174.437445536289</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>-36.88369284547562,174.43715233438564</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>-36.8830190442708,174.43688740509373</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>-36.88233533977511,174.43665933731364</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>-36.88167241043096,174.4363540773243</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>-36.8859380826675,174.43690457226043</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>-36.88504590896369,174.43774677321736</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>-36.88436023073861,174.43746653448886</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>-36.88368932320213,174.4371684663734</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>-36.883014988975205,174.43690334176418</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>-36.882336204517884,174.43665638605995</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>-36.88167378666964,174.43634992945422</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>-36.88593484326146,174.43692218051697</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>-36.88504433949901,174.43775530380628</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>-36.88435797717158,174.4374787834377</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>-36.88368653374911,174.43718124204042</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>-36.883014852891435,174.43690387655175</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>-36.88233422796287,174.43666313178258</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>-36.88167578221549,174.43634391504233</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>-36.8859330122917,174.43693213300912</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>-36.88504431937768,174.43775541317282</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>-36.88435689062988,174.43748468918065</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>-36.883684926267094,174.43718860428876</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>-36.88301545166004,174.43690152348643</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>-36.88233435149757,174.43666271017494</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>-36.88167918840511,174.43633364906265</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0182/nzd0182.xlsx
+++ b/data/nzd0182/nzd0182.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I586"/>
+  <dimension ref="A1:I588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19690,6 +19690,72 @@
       <c r="I586" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>465.26</v>
+      </c>
+      <c r="C587" t="n">
+        <v>371.37</v>
+      </c>
+      <c r="D587" t="n">
+        <v>379.34</v>
+      </c>
+      <c r="E587" t="n">
+        <v>389.78</v>
+      </c>
+      <c r="F587" t="n">
+        <v>392.38</v>
+      </c>
+      <c r="G587" t="n">
+        <v>391.16</v>
+      </c>
+      <c r="H587" t="n">
+        <v>390.34</v>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>461.11</v>
+      </c>
+      <c r="C588" t="n">
+        <v>369.2</v>
+      </c>
+      <c r="D588" t="n">
+        <v>376.25</v>
+      </c>
+      <c r="E588" t="n">
+        <v>388.68</v>
+      </c>
+      <c r="F588" t="n">
+        <v>392.76</v>
+      </c>
+      <c r="G588" t="n">
+        <v>392.59</v>
+      </c>
+      <c r="H588" t="n">
+        <v>394.06</v>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -19704,7 +19770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B633"/>
+  <dimension ref="A1:B635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26037,6 +26103,26 @@
       </c>
       <c r="B633" t="n">
         <v>1.52</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>0.16</v>
       </c>
     </row>
   </sheetData>
@@ -26205,28 +26291,28 @@
         <v>0.0154</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06541900454545291</v>
+        <v>0.07050089209738844</v>
       </c>
       <c r="J2" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K2" t="n">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001762409786111307</v>
+        <v>0.0002061885014211784</v>
       </c>
       <c r="M2" t="n">
-        <v>31.57900171589796</v>
+        <v>31.49253445874027</v>
       </c>
       <c r="N2" t="n">
-        <v>1522.016676844012</v>
+        <v>1516.694090762736</v>
       </c>
       <c r="O2" t="n">
-        <v>39.01303214111935</v>
+        <v>38.94475690979128</v>
       </c>
       <c r="P2" t="n">
-        <v>453.6832979652541</v>
+        <v>453.6324467209404</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26283,28 +26369,28 @@
         <v>0.0462</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8424410365465288</v>
+        <v>0.8590762014858191</v>
       </c>
       <c r="J3" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K3" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2934305254808601</v>
+        <v>0.2987481740091792</v>
       </c>
       <c r="M3" t="n">
-        <v>8.363161652028003</v>
+        <v>8.428770000605729</v>
       </c>
       <c r="N3" t="n">
-        <v>102.8388336919588</v>
+        <v>104.6835730256184</v>
       </c>
       <c r="O3" t="n">
-        <v>10.14094836255263</v>
+        <v>10.23149906052962</v>
       </c>
       <c r="P3" t="n">
-        <v>322.150282998593</v>
+        <v>321.9821686792847</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26361,28 +26447,28 @@
         <v>0.05</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9078710171888338</v>
+        <v>0.9291810651955237</v>
       </c>
       <c r="J4" t="n">
+        <v>587</v>
+      </c>
+      <c r="K4" t="n">
         <v>585</v>
       </c>
-      <c r="K4" t="n">
-        <v>583</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.3096020624344875</v>
+        <v>0.3143035072923703</v>
       </c>
       <c r="M4" t="n">
-        <v>8.050485894447283</v>
+        <v>8.165538063317026</v>
       </c>
       <c r="N4" t="n">
-        <v>109.9434317061451</v>
+        <v>113.1437986271641</v>
       </c>
       <c r="O4" t="n">
-        <v>10.48539134730531</v>
+        <v>10.63690738077399</v>
       </c>
       <c r="P4" t="n">
-        <v>320.8942901905784</v>
+        <v>320.677884779503</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26439,28 +26525,28 @@
         <v>0.057</v>
       </c>
       <c r="I5" t="n">
-        <v>1.032990760395662</v>
+        <v>1.056779610928006</v>
       </c>
       <c r="J5" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K5" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3785496422868693</v>
+        <v>0.381258101170078</v>
       </c>
       <c r="M5" t="n">
-        <v>7.640214505323305</v>
+        <v>7.750000588810722</v>
       </c>
       <c r="N5" t="n">
-        <v>104.7336995238627</v>
+        <v>108.8168586356879</v>
       </c>
       <c r="O5" t="n">
-        <v>10.2339483838772</v>
+        <v>10.43153194098009</v>
       </c>
       <c r="P5" t="n">
-        <v>325.1795056056022</v>
+        <v>324.9379981303533</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26517,28 +26603,28 @@
         <v>0.0359</v>
       </c>
       <c r="I6" t="n">
-        <v>1.027707846655009</v>
+        <v>1.050930392226737</v>
       </c>
       <c r="J6" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K6" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3087861512498975</v>
+        <v>0.3136585604474601</v>
       </c>
       <c r="M6" t="n">
-        <v>9.492556176956191</v>
+        <v>9.578613730106049</v>
       </c>
       <c r="N6" t="n">
-        <v>141.3526417699485</v>
+        <v>145.1001521521914</v>
       </c>
       <c r="O6" t="n">
-        <v>11.88918171153711</v>
+        <v>12.04575245271923</v>
       </c>
       <c r="P6" t="n">
-        <v>329.5287695968746</v>
+        <v>329.2930016141845</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26595,28 +26681,28 @@
         <v>0.0523</v>
       </c>
       <c r="I7" t="n">
-        <v>1.086985574208206</v>
+        <v>1.112637245304994</v>
       </c>
       <c r="J7" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K7" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2540142856688444</v>
+        <v>0.2596534395070536</v>
       </c>
       <c r="M7" t="n">
-        <v>11.40337302390657</v>
+        <v>11.5133212814621</v>
       </c>
       <c r="N7" t="n">
-        <v>208.4921908371671</v>
+        <v>212.9807554652641</v>
       </c>
       <c r="O7" t="n">
-        <v>14.43925866646786</v>
+        <v>14.59386019753732</v>
       </c>
       <c r="P7" t="n">
-        <v>323.3674409007422</v>
+        <v>323.1080360977242</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26673,28 +26759,28 @@
         <v>0.0454</v>
       </c>
       <c r="I8" t="n">
-        <v>1.195006714421148</v>
+        <v>1.217740766926371</v>
       </c>
       <c r="J8" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K8" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2633635402243283</v>
+        <v>0.2689075519639789</v>
       </c>
       <c r="M8" t="n">
-        <v>12.34474092112029</v>
+        <v>12.40205458613409</v>
       </c>
       <c r="N8" t="n">
-        <v>238.8076407708864</v>
+        <v>242.0560140658578</v>
       </c>
       <c r="O8" t="n">
-        <v>15.45340223934155</v>
+        <v>15.55814944220095</v>
       </c>
       <c r="P8" t="n">
-        <v>325.4115684587705</v>
+        <v>325.1807376668769</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26732,7 +26818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I586"/>
+  <dimension ref="A1:I588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54097,6 +54183,100 @@
         </is>
       </c>
     </row>
+    <row r="587">
+      <c r="A587" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>-36.88593379699313,174.43692786765538</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>-36.88504301148996,174.43776252199666</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>-36.88435717232591,174.43748315806212</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>-36.88368677014349,174.4371801593568</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>-36.883017329615875,174.4368941434177</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>-36.88233867521111,174.43664795390612</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>-36.881681321573936,174.43632721986282</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>-36.885925446957316,174.4369732553889</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>-36.88503864515411,174.4377862545297</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>-36.88435095488773,174.4375169520324</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>-36.88368416980482,174.4371920688761</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>-36.88301836385222,174.43689007903185</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>-36.8823430915738,174.4366328814298</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>-36.88169412057969,174.43628864465592</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
